--- a/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="163">
   <si>
     <t>Filename</t>
   </si>
@@ -464,7 +464,7 @@
     <t>l</t>
   </si>
   <si>
-    <t>sac-seq</t>
+    <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
     <t>Metabolomics Workbench</t>
@@ -476,7 +476,7 @@
     <t>PCRfree</t>
   </si>
   <si>
-    <t>Smart-seq1</t>
+    <t>sac-seq</t>
   </si>
   <si>
     <t>MGnify</t>
@@ -488,7 +488,7 @@
     <t>polyAselection</t>
   </si>
   <si>
-    <t>Smart-seq2</t>
+    <t>Smart-seq1</t>
   </si>
   <si>
     <t>NCBI Gene</t>
@@ -500,10 +500,7 @@
     <t>proximity ligation</t>
   </si>
   <si>
-    <t>Smart-seq4</t>
-  </si>
-  <si>
-    <t>PRIDE</t>
+    <t>Smart-seq2</t>
   </si>
   <si>
     <t>mg/l</t>
@@ -512,10 +509,7 @@
     <t>rRNAdepletion</t>
   </si>
   <si>
-    <t>SMRTbell</t>
-  </si>
-  <si>
-    <t>SRA</t>
+    <t>Smart-seq4</t>
   </si>
   <si>
     <t>mg/ml</t>
@@ -524,10 +518,7 @@
     <t>snIsoSeq</t>
   </si>
   <si>
-    <t>TruSeq</t>
-  </si>
-  <si>
-    <t>UniProt</t>
+    <t>SMRTbell</t>
   </si>
   <si>
     <t>miu/ml</t>
@@ -536,7 +527,7 @@
     <t>SPLITseq</t>
   </si>
   <si>
-    <t>Ultralow Methyl-Seq</t>
+    <t>TruSeq</t>
   </si>
   <si>
     <t>ml</t>
@@ -545,10 +536,19 @@
     <t>STARRSeq</t>
   </si>
   <si>
+    <t>Ultralow Methyl-Seq</t>
+  </si>
+  <si>
+    <t>PRIDE</t>
+  </si>
+  <si>
     <t>mM</t>
   </si>
   <si>
     <t>SureCell</t>
+  </si>
+  <si>
+    <t>SRA</t>
   </si>
   <si>
     <t>MOI</t>
@@ -557,7 +557,13 @@
     <t>totalRNA</t>
   </si>
   <si>
+    <t>Synapse</t>
+  </si>
+  <si>
     <t>ng</t>
+  </si>
+  <si>
+    <t>UniProt</t>
   </si>
   <si>
     <t>ng/dl</t>
@@ -31042,6 +31048,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$56</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$27</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
       <formula1>Sheet2!$I$2:$I$10</formula1>
     </dataValidation>
@@ -31051,12 +31060,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="Z2:Z1000">
       <formula1>Sheet2!$Z$2:$Z$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="T2:T1000">
-      <formula1>Sheet2!$T$2:$T$22</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$21</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$3</formula1>
     </dataValidation>
@@ -31065,6 +31068,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="T2:T1000">
+      <formula1>Sheet2!$T$2:$T$23</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -31507,66 +31513,78 @@
     </row>
     <row r="19">
       <c r="H19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="S19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="T19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="T19" s="6" t="s">
+    </row>
+    <row r="20">
+      <c r="H20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="6" t="s">
+      <c r="S20" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="T20" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="S20" s="6" t="s">
+    </row>
+    <row r="21">
+      <c r="H21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N21" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="T20" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="N21" s="6" t="s">
+    </row>
+    <row r="22">
+      <c r="H22" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="N22" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="S22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="T22" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22">
-      <c r="N22" s="6" t="s">
+    <row r="23">
+      <c r="H23" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="N23" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="T22" s="6" t="s">
+      <c r="S23" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="T23" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23">
-      <c r="N23" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="S23" s="6" t="s">
+    <row r="24">
+      <c r="H24" s="6" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="24">
       <c r="N24" s="6" t="s">
         <v>129</v>
       </c>
@@ -31575,41 +31593,50 @@
       </c>
     </row>
     <row r="25">
+      <c r="H25" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="N25" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="26">
-      <c r="N26" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="N27" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>133</v>
       </c>
+      <c r="N26" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="28">
       <c r="N28" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="N29" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30">
       <c r="N30" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="N31" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32">
@@ -31619,12 +31646,12 @@
     </row>
     <row r="33">
       <c r="N33" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="N34" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35">
@@ -31634,107 +31661,107 @@
     </row>
     <row r="36">
       <c r="N36" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
       <c r="N37" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38">
       <c r="N38" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39">
       <c r="N39" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40">
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41">
       <c r="N41" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42">
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43">
       <c r="N43" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44">
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45">
       <c r="N45" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46">
       <c r="N46" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47">
       <c r="N47" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49">
       <c r="N49" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50">
       <c r="N50" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51">
       <c r="N51" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52">
       <c r="N52" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53">
       <c r="N53" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54">
       <c r="N54" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55">
       <c r="N55" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56">
       <c r="N56" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="164">
   <si>
     <t>Filename</t>
   </si>
@@ -395,7 +395,7 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>GENCODEv38 GRCh38</t>
+    <t>GENCODEv38</t>
   </si>
   <si>
     <t>total RNA minus rRNA</t>
@@ -431,7 +431,7 @@
     <t>multiome</t>
   </si>
   <si>
-    <t>IEDB</t>
+    <t>GRCh38</t>
   </si>
   <si>
     <t>IU/ml</t>
@@ -440,7 +440,7 @@
     <t>MULTIseq</t>
   </si>
   <si>
-    <t>ImmPort</t>
+    <t>IEDB</t>
   </si>
   <si>
     <t>Kallikrein Inactivator Unit per Milliliter</t>
@@ -449,7 +449,7 @@
     <t>Omni-ATAC</t>
   </si>
   <si>
-    <t>MassIVE</t>
+    <t>ImmPort</t>
   </si>
   <si>
     <t>kg</t>
@@ -458,7 +458,7 @@
     <t>Qiagen PreAnalytiX PAXgene Blood miRNA Kit</t>
   </si>
   <si>
-    <t>MetaboLights</t>
+    <t>MassIVE</t>
   </si>
   <si>
     <t>l</t>
@@ -467,7 +467,7 @@
     <t>Qiagen Rneasy Extraction Kit</t>
   </si>
   <si>
-    <t>Metabolomics Workbench</t>
+    <t>MetaboLights</t>
   </si>
   <si>
     <t>M</t>
@@ -479,7 +479,7 @@
     <t>sac-seq</t>
   </si>
   <si>
-    <t>MGnify</t>
+    <t>Metabolomics Workbench</t>
   </si>
   <si>
     <t>mg</t>
@@ -491,7 +491,7 @@
     <t>Smart-seq1</t>
   </si>
   <si>
-    <t>NCBI Gene</t>
+    <t>MGnify</t>
   </si>
   <si>
     <t>mg/dl</t>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>Smart-seq2</t>
+  </si>
+  <si>
+    <t>NCBI Gene</t>
   </si>
   <si>
     <t>mg/l</t>
@@ -539,16 +542,13 @@
     <t>Ultralow Methyl-Seq</t>
   </si>
   <si>
-    <t>PRIDE</t>
-  </si>
-  <si>
     <t>mM</t>
   </si>
   <si>
     <t>SureCell</t>
   </si>
   <si>
-    <t>SRA</t>
+    <t>PRIDE</t>
   </si>
   <si>
     <t>MOI</t>
@@ -557,16 +557,19 @@
     <t>totalRNA</t>
   </si>
   <si>
-    <t>Synapse</t>
+    <t>SRA</t>
   </si>
   <si>
     <t>ng</t>
   </si>
   <si>
-    <t>UniProt</t>
+    <t>Synapse</t>
   </si>
   <si>
     <t>ng/dl</t>
+  </si>
+  <si>
+    <t>UniProt</t>
   </si>
   <si>
     <t>ng/ml</t>
@@ -31052,9 +31055,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="N2:N1000">
       <formula1>Sheet2!$N$2:$N$56</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
-      <formula1>Sheet2!$H$2:$H$27</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="I2:I1000">
       <formula1>Sheet2!$I$2:$I$10</formula1>
     </dataValidation>
@@ -31069,6 +31069,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="W2:W1000">
       <formula1>Sheet2!$W$2:$W$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
+      <formula1>Sheet2!$H$2:$H$28</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="J2:J1000">
       <formula1>Sheet2!$J$2:$J$9</formula1>
@@ -31517,63 +31520,63 @@
     </row>
     <row r="19">
       <c r="H19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="T19" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="N19" s="6" t="s">
-        <v>113</v>
+      <c r="N20" s="6" t="s">
+        <v>117</v>
       </c>
-      <c r="S19" s="6" t="s">
-        <v>114</v>
+      <c r="S20" s="6" t="s">
+        <v>118</v>
       </c>
-      <c r="T19" s="6" t="s">
-        <v>115</v>
+      <c r="T20" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" s="6" t="s">
+    <row r="21">
+      <c r="H21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="N20" s="6" t="s">
-        <v>116</v>
+      <c r="N21" s="6" t="s">
+        <v>120</v>
       </c>
-      <c r="S20" s="6" t="s">
-        <v>117</v>
+      <c r="S21" s="6" t="s">
+        <v>121</v>
       </c>
-      <c r="T20" s="6" t="s">
-        <v>118</v>
+      <c r="T21" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" s="6" t="s">
+    <row r="22">
+      <c r="H22" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="N21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="T21" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="N22" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="T22" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23">
       <c r="H23" s="6" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>126</v>
@@ -31617,30 +31620,33 @@
     </row>
     <row r="27">
       <c r="H27" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N27" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28">
       <c r="N28" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="N29" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="N30" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
       <c r="N31" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
@@ -31650,12 +31656,12 @@
     </row>
     <row r="33">
       <c r="N33" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34">
       <c r="N34" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35">
@@ -31665,107 +31671,107 @@
     </row>
     <row r="36">
       <c r="N36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37">
       <c r="N37" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38">
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39">
       <c r="N39" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40">
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41">
       <c r="N41" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42">
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
       <c r="N43" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44">
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45">
       <c r="N45" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46">
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47">
       <c r="N47" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48">
       <c r="N48" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
       <c r="N49" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50">
       <c r="N50" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51">
       <c r="N51" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52">
       <c r="N52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53">
       <c r="N53" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54">
       <c r="N54" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55">
       <c r="N55" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="N56" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="163">
   <si>
     <t>Filename</t>
   </si>
@@ -371,7 +371,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>singleEnd pairedEnd</t>
+    <t>Unknown</t>
   </si>
   <si>
     <t>GenBank</t>
@@ -390,9 +390,6 @@
   </si>
   <si>
     <t>NEBNext</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>GENCODEv38</t>
@@ -31061,9 +31058,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="S2:S1000">
       <formula1>Sheet2!$S$2:$S$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="Z2:Z1000">
-      <formula1>Sheet2!$Z$2:$Z$8</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="V2:V1000">
       <formula1>Sheet2!$V$2:$V$3</formula1>
     </dataValidation>
@@ -31078,6 +31072,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="T2:T1000">
       <formula1>Sheet2!$T$2:$T$23</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Choose one from dropdown" sqref="Z2:Z1000">
+      <formula1>Sheet2!$Z$2:$Z$7</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -31360,47 +31357,44 @@
         <v>75</v>
       </c>
       <c r="W8" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="Z8" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="N9" s="6" t="s">
+      <c r="S9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="W9" s="6" t="s">
+    </row>
+    <row r="10">
+      <c r="H10" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="N10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>37</v>
@@ -31408,13 +31402,13 @@
     </row>
     <row r="11">
       <c r="H11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="S11" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>44</v>
@@ -31422,13 +31416,13 @@
     </row>
     <row r="12">
       <c r="H12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="S12" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>49</v>
@@ -31436,100 +31430,100 @@
     </row>
     <row r="13">
       <c r="H13" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T13" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" s="6" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="H14" s="6" t="s">
+      <c r="N14" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>44</v>
       </c>
       <c r="T14" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="6" t="s">
+      <c r="N15" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="T15" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="H16" s="6" t="s">
+      <c r="N16" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="S16" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="S16" s="6" t="s">
+      <c r="T16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="T16" s="6" t="s">
+    </row>
+    <row r="17">
+      <c r="H17" s="6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="H17" s="6" t="s">
+      <c r="N17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="S17" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="S17" s="6" t="s">
+      <c r="T17" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="T17" s="6" t="s">
+    </row>
+    <row r="18">
+      <c r="H18" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="H18" s="6" t="s">
+      <c r="N18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="S18" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="S18" s="6" t="s">
+      <c r="T18" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="T18" s="6" t="s">
+    </row>
+    <row r="19">
+      <c r="H19" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="6" t="s">
+      <c r="N19" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="S19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="T19" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="T19" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="20">
@@ -31537,13 +31531,13 @@
         <v>37</v>
       </c>
       <c r="N20" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="S20" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="S20" s="6" t="s">
+      <c r="T20" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="T20" s="6" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21">
@@ -31551,13 +31545,13 @@
         <v>44</v>
       </c>
       <c r="N21" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="S21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="T21" s="6" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -31565,13 +31559,13 @@
         <v>49</v>
       </c>
       <c r="N22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="S22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="T22" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="T22" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="23">
@@ -31579,74 +31573,74 @@
         <v>63</v>
       </c>
       <c r="N23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="S23" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="S23" s="6" t="s">
+      <c r="T23" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="T23" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="H24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="S24" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="S24" s="6" t="s">
+    </row>
+    <row r="25">
+      <c r="H25" s="6" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="H25" s="6" t="s">
+      <c r="N25" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="S25" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="S25" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="H26" s="6" t="s">
+      <c r="N26" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="N26" s="6" t="s">
+    </row>
+    <row r="27">
+      <c r="H27" s="6" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="H27" s="6" t="s">
+      <c r="N27" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="N27" s="6" t="s">
+    </row>
+    <row r="28">
+      <c r="H28" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="28">
-      <c r="H28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="N28" s="6" t="s">
+    <row r="29">
+      <c r="N29" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="29">
-      <c r="N29" s="6" t="s">
+    <row r="30">
+      <c r="N30" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30">
-      <c r="N30" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
     <row r="31">
       <c r="N31" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32">
@@ -31656,12 +31650,12 @@
     </row>
     <row r="33">
       <c r="N33" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
       <c r="N34" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35">
@@ -31671,107 +31665,107 @@
     </row>
     <row r="36">
       <c r="N36" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="N37" s="6" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="37">
-      <c r="N37" s="6" t="s">
+    <row r="38">
+      <c r="N38" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="38">
-      <c r="N38" s="6" t="s">
+    <row r="39">
+      <c r="N39" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="39">
-      <c r="N39" s="6" t="s">
+    <row r="40">
+      <c r="N40" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="40">
-      <c r="N40" s="6" t="s">
+    <row r="41">
+      <c r="N41" s="6" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="41">
-      <c r="N41" s="6" t="s">
+    <row r="42">
+      <c r="N42" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="42">
-      <c r="N42" s="6" t="s">
+    <row r="43">
+      <c r="N43" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="43">
-      <c r="N43" s="6" t="s">
+    <row r="44">
+      <c r="N44" s="6" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="44">
-      <c r="N44" s="6" t="s">
+    <row r="45">
+      <c r="N45" s="6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="45">
-      <c r="N45" s="6" t="s">
+    <row r="46">
+      <c r="N46" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46">
-      <c r="N46" s="6" t="s">
+    <row r="47">
+      <c r="N47" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="47">
-      <c r="N47" s="6" t="s">
+    <row r="48">
+      <c r="N48" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="48">
-      <c r="N48" s="6" t="s">
+    <row r="49">
+      <c r="N49" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="49">
-      <c r="N49" s="6" t="s">
+    <row r="50">
+      <c r="N50" s="6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="50">
-      <c r="N50" s="6" t="s">
+    <row r="51">
+      <c r="N51" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="51">
-      <c r="N51" s="6" t="s">
+    <row r="52">
+      <c r="N52" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="52">
-      <c r="N52" s="6" t="s">
+    <row r="53">
+      <c r="N53" s="6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="53">
-      <c r="N53" s="6" t="s">
+    <row r="54">
+      <c r="N54" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="54">
-      <c r="N54" s="6" t="s">
+    <row r="55">
+      <c r="N55" s="6" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="55">
-      <c r="N55" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
     <row r="56">
       <c r="N56" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayScRNAseqTemplate.xlsx
@@ -275,7 +275,7 @@
     <t>forward</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>Broad Single Cell Portal</t>
@@ -296,7 +296,7 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>dbGAP</t>
@@ -371,7 +371,7 @@
     <t>stranded</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>GenBank</t>
